--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-health-professional.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-lm-health-professional.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="102">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,126 +250,83 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-health-professional.personne</t>
+    <t>fr-lm-health-professional.identifier</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiant.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-human-name
+</t>
+  </si>
+  <si>
+    <t>Nom du professionnel de santé.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Address
+</t>
+  </si>
+  <si>
+    <t>Adresses géopostales du professionnel de santé.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint
+</t>
+  </si>
+  <si>
+    <t>Coordonnées télécom du professionnel de santé.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.professionalRole</t>
   </si>
   <si>
     <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Personne</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.identifiantPersonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiant de la personne.
-- obligatoire pour les professionnels et les patients.</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.roleFonctionnel</t>
+    <t>Rôle professionnel</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.professionalRole.role</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Rôle fonctionnel</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.dateExecution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date de l’exécution</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.professionRole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- Profession pour les professionnels.
-- Rôle pour les non professionnels.</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.lien</t>
-  </si>
-  <si>
-    <t>Lien de la personne avec le patient/usager</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.adresse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address
-</t>
-  </si>
-  <si>
-    <t>Adresse géopostale</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.coordonneesTelecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
-</t>
-  </si>
-  <si>
-    <t>Coordonnées télécom</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.IdentitePersonne</t>
-  </si>
-  <si>
-    <t>Identité de la personne</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.IdentitePersonne.nomPersonne</t>
-  </si>
-  <si>
-    <t>Nom de la personne</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.IdentitePersonne.prenomPersonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Prénom de la personne</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.IdentitePersonne.civilite</t>
-  </si>
-  <si>
-    <t>Civilité</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.IdentitePersonne.titre</t>
-  </si>
-  <si>
-    <t>Titre</t>
-  </si>
-  <si>
-    <t>fr-lm-health-professional.personne.structure</t>
+    <t>Rôle du professionnel de santé.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.professionalRole.organisation</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
 </t>
   </si>
   <si>
-    <t>Structure</t>
+    <t>Organisation à laquelle le professionnel de santé est rattaché pour exercer ce rôle.</t>
+  </si>
+  <si>
+    <t>fr-lm-health-professional.professionalRole.specialty</t>
+  </si>
+  <si>
+    <t>Spécialité d'un professionnel de santé qui décrit le rôle fonctionnel qu'il exerce au sein de l'organisation.</t>
   </si>
 </sst>
 </file>
@@ -671,11 +628,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.91015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.91015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.10546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.10546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -684,7 +641,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.56640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.28125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -705,7 +662,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="55.91015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="44.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1137,7 +1094,7 @@
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1212,7 +1169,7 @@
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1234,10 +1191,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1309,10 +1266,10 @@
         <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1337,7 +1294,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1349,13 +1306,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1412,7 +1369,7 @@
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1423,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1437,7 +1394,7 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1449,13 +1406,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1506,13 +1463,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1523,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1537,7 +1494,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1549,13 +1506,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1606,13 +1563,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1623,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1649,13 +1606,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1706,7 +1663,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1718,606 +1675,6 @@
         <v>73</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K11" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
         <v>73</v>
       </c>
     </row>
